--- a/artfynd/A 568-2025 artfynd.xlsx
+++ b/artfynd/A 568-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102248208</v>
+        <v>105311999</v>
       </c>
       <c r="B2" t="n">
-        <v>5112</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102204</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nordanstig, Hls</t>
+          <t>Hälleberget, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612147.3266138983</v>
+        <v>612562</v>
       </c>
       <c r="R2" t="n">
-        <v>6866610.451650858</v>
+        <v>6866962</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,26 +743,11 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår på död grangren.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,11 +756,16 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -795,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105316175</v>
+        <v>105312000</v>
       </c>
       <c r="B3" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612180.2906507243</v>
+        <v>612529</v>
       </c>
       <c r="R3" t="n">
-        <v>6866770.879250377</v>
+        <v>6866897</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,19 +845,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105312025</v>
+        <v>105312002</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612418.2752730902</v>
+        <v>612461</v>
       </c>
       <c r="R4" t="n">
-        <v>6866998.865411165</v>
+        <v>6866851</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -985,19 +947,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105311998</v>
+        <v>105312003</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612563.3768337772</v>
+        <v>612407</v>
       </c>
       <c r="R5" t="n">
-        <v>6866993.75512823</v>
+        <v>6866855</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,19 +1049,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105312020</v>
+        <v>105312006</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1162,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>612262.3981828068</v>
+        <v>612391</v>
       </c>
       <c r="R6" t="n">
-        <v>6866843.823027246</v>
+        <v>6866871</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,19 +1151,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105312005</v>
+        <v>105312008</v>
       </c>
       <c r="B7" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1303,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>612388.985195449</v>
+        <v>612246</v>
       </c>
       <c r="R7" t="n">
-        <v>6866870.622101887</v>
+        <v>6866728</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1336,19 +1253,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105312019</v>
+        <v>105312011</v>
       </c>
       <c r="B8" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>612237.6824133168</v>
+        <v>612146</v>
       </c>
       <c r="R8" t="n">
-        <v>6866834.523737852</v>
+        <v>6866604</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1453,19 +1355,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105312018</v>
+        <v>105312015</v>
       </c>
       <c r="B9" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>612211.4652362497</v>
+        <v>612162</v>
       </c>
       <c r="R9" t="n">
-        <v>6866842.145933688</v>
+        <v>6866772</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1570,19 +1457,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,37 +1491,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105315309</v>
+        <v>105312016</v>
       </c>
       <c r="B10" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1654,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>612477.8970338507</v>
+        <v>612181</v>
       </c>
       <c r="R10" t="n">
-        <v>6867037.600593894</v>
+        <v>6866814</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1687,21 +1559,11 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1710,11 +1572,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>På klen granlåga</t>
-        </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -1736,15 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105312021</v>
+        <v>105312018</v>
       </c>
       <c r="B11" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,21 +1604,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1776,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>612297.2563163198</v>
+        <v>612211</v>
       </c>
       <c r="R11" t="n">
-        <v>6866860.527718632</v>
+        <v>6866842</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1809,19 +1661,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,15 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105312006</v>
+        <v>105312019</v>
       </c>
       <c r="B12" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1893,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>612390.8715863572</v>
+        <v>612238</v>
       </c>
       <c r="R12" t="n">
-        <v>6866870.684301288</v>
+        <v>6866835</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1926,19 +1763,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1970,37 +1797,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105312017</v>
+        <v>105312024</v>
       </c>
       <c r="B13" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2010,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>612199.6221062175</v>
+        <v>612408</v>
       </c>
       <c r="R13" t="n">
-        <v>6866829.028027236</v>
+        <v>6866982</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2043,21 +1865,11 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2066,11 +1878,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>På asp</t>
-        </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -2092,15 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105312012</v>
+        <v>105312029</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,21 +1910,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2132,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>612149.6966255942</v>
+        <v>612532</v>
       </c>
       <c r="R14" t="n">
-        <v>6866667.573351199</v>
+        <v>6867076</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2165,19 +1967,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2209,15 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105312026</v>
+        <v>105312030</v>
       </c>
       <c r="B15" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2225,21 +2012,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2249,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>612426.0492465588</v>
+        <v>612532</v>
       </c>
       <c r="R15" t="n">
-        <v>6867020.805657836</v>
+        <v>6867137</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2282,19 +2069,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2326,15 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>105315306</v>
+        <v>105312032</v>
       </c>
       <c r="B16" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2342,21 +2114,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2366,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>612453.5208559125</v>
+        <v>612545</v>
       </c>
       <c r="R16" t="n">
-        <v>6866846.351727937</v>
+        <v>6867140</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2399,19 +2171,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2443,15 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>105312008</v>
+        <v>105312005</v>
       </c>
       <c r="B17" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,21 +2216,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2483,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>612245.9183924417</v>
+        <v>612389</v>
       </c>
       <c r="R17" t="n">
-        <v>6866727.783228802</v>
+        <v>6866871</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2516,19 +2273,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2560,37 +2307,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>105312027</v>
+        <v>105315308</v>
       </c>
       <c r="B18" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6426</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2600,10 +2342,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>612470.7923364562</v>
+        <v>612241</v>
       </c>
       <c r="R18" t="n">
-        <v>6867038.308910745</v>
+        <v>6866836</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2633,21 +2375,11 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2659,7 +2391,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>På klen död gran vid lodyta.</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -2682,37 +2414,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>105316176</v>
+        <v>105315304</v>
       </c>
       <c r="B19" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2722,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>612513.8093906725</v>
+        <v>612555</v>
       </c>
       <c r="R19" t="n">
-        <v>6867065.18334777</v>
+        <v>6866994</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2755,21 +2482,11 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2778,11 +2495,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Spår</t>
-        </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
@@ -2804,15 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>105312002</v>
+        <v>105315305</v>
       </c>
       <c r="B20" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2820,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2844,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>612461.382710451</v>
+        <v>612462</v>
       </c>
       <c r="R20" t="n">
-        <v>6866851.325209416</v>
+        <v>6866848</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2877,19 +2584,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2921,15 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>105312022</v>
+        <v>105315306</v>
       </c>
       <c r="B21" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2937,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2961,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>612298.0754025793</v>
+        <v>612454</v>
       </c>
       <c r="R21" t="n">
-        <v>6866864.325956702</v>
+        <v>6866846</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2994,19 +2686,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3038,37 +2720,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>105312028</v>
+        <v>105315307</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3078,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>612497.7862008068</v>
+        <v>612185</v>
       </c>
       <c r="R22" t="n">
-        <v>6867050.041598381</v>
+        <v>6866829</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3111,19 +2788,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3155,37 +2822,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>105311997</v>
+        <v>105315309</v>
       </c>
       <c r="B23" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3195,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>612562.1432692775</v>
+        <v>612478</v>
       </c>
       <c r="R23" t="n">
-        <v>6867016.812485723</v>
+        <v>6867038</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3228,21 +2890,11 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3251,6 +2903,11 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>På klen granlåga</t>
+        </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
@@ -3272,37 +2929,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>105312007</v>
+        <v>105315310</v>
       </c>
       <c r="B24" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3312,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>612312.9436146641</v>
+        <v>612475</v>
       </c>
       <c r="R24" t="n">
-        <v>6866785.618636707</v>
+        <v>6867042</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3345,21 +2997,11 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3368,6 +3010,11 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
+        </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
@@ -3389,37 +3036,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>105312032</v>
+        <v>105311997</v>
       </c>
       <c r="B25" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3429,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>612544.849804837</v>
+        <v>612562</v>
       </c>
       <c r="R25" t="n">
-        <v>6867140.21422032</v>
+        <v>6867017</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3462,19 +3104,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3506,37 +3138,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>105312016</v>
+        <v>105311998</v>
       </c>
       <c r="B26" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3546,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>612180.7667997268</v>
+        <v>612563</v>
       </c>
       <c r="R26" t="n">
-        <v>6866813.793688045</v>
+        <v>6866994</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3579,19 +3206,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3623,37 +3240,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>105316174</v>
+        <v>105312001</v>
       </c>
       <c r="B27" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3663,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>612395.1625479551</v>
+        <v>612478</v>
       </c>
       <c r="R27" t="n">
-        <v>6866869.411570089</v>
+        <v>6866873</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3696,21 +3308,11 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3719,11 +3321,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Spår</t>
-        </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
@@ -3745,37 +3342,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>105311999</v>
+        <v>105312007</v>
       </c>
       <c r="B28" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3785,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>612562.0763641258</v>
+        <v>612313</v>
       </c>
       <c r="R28" t="n">
-        <v>6866961.657422092</v>
+        <v>6866786</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3818,19 +3410,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3862,37 +3444,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>105312004</v>
+        <v>105312009</v>
       </c>
       <c r="B29" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3902,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>612405.0603670642</v>
+        <v>612237</v>
       </c>
       <c r="R29" t="n">
-        <v>6866855.595726727</v>
+        <v>6866698</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3935,19 +3512,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3979,37 +3546,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>105312030</v>
+        <v>105312010</v>
       </c>
       <c r="B30" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4019,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>612531.7238396265</v>
+        <v>612211</v>
       </c>
       <c r="R30" t="n">
-        <v>6867137.423951326</v>
+        <v>6866664</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4052,19 +3614,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4096,37 +3648,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>105312013</v>
+        <v>105312012</v>
       </c>
       <c r="B31" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4136,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>612191.2749701499</v>
+        <v>612150</v>
       </c>
       <c r="R31" t="n">
-        <v>6866695.341617185</v>
+        <v>6866668</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4169,21 +3716,11 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4192,11 +3729,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
@@ -4218,19 +3750,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>105312023</v>
+        <v>105312014</v>
       </c>
       <c r="B32" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4258,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>612374.3483717513</v>
+        <v>612190</v>
       </c>
       <c r="R32" t="n">
-        <v>6866942.263933114</v>
+        <v>6866764</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4291,19 +3818,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4335,37 +3852,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>105312000</v>
+        <v>105312020</v>
       </c>
       <c r="B33" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4375,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>612528.7905924792</v>
+        <v>612262</v>
       </c>
       <c r="R33" t="n">
-        <v>6866897.390763992</v>
+        <v>6866844</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4408,19 +3920,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4452,37 +3954,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>105315308</v>
+        <v>105312022</v>
       </c>
       <c r="B34" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4492,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>612241.4242212975</v>
+        <v>612298</v>
       </c>
       <c r="R34" t="n">
-        <v>6866835.589768198</v>
+        <v>6866864</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4525,21 +4022,11 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4548,11 +4035,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
@@ -4574,19 +4056,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>105312014</v>
+        <v>105312023</v>
       </c>
       <c r="B35" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4614,10 +4091,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>612190.4269710722</v>
+        <v>612374</v>
       </c>
       <c r="R35" t="n">
-        <v>6866764.14157367</v>
+        <v>6866942</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4647,19 +4124,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4691,37 +4158,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>105312029</v>
+        <v>105312025</v>
       </c>
       <c r="B36" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4731,10 +4193,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>612532.3302025485</v>
+        <v>612418</v>
       </c>
       <c r="R36" t="n">
-        <v>6867076.165165142</v>
+        <v>6866999</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4764,19 +4226,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4808,37 +4260,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>105312011</v>
+        <v>105312026</v>
       </c>
       <c r="B37" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4848,10 +4295,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>612145.6569759632</v>
+        <v>612426</v>
       </c>
       <c r="R37" t="n">
-        <v>6866603.796561057</v>
+        <v>6867021</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4881,19 +4328,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4925,37 +4362,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>105315307</v>
+        <v>105312028</v>
       </c>
       <c r="B38" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4965,10 +4397,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>612184.5153035307</v>
+        <v>612498</v>
       </c>
       <c r="R38" t="n">
-        <v>6866829.002209808</v>
+        <v>6867050</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4998,19 +4430,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5042,37 +4464,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>105310363</v>
+        <v>105312027</v>
       </c>
       <c r="B39" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5082,10 +4499,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>612555.5414621616</v>
+        <v>612471</v>
       </c>
       <c r="R39" t="n">
-        <v>6866973.697883114</v>
+        <v>6867038</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5115,21 +4532,11 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5141,7 +4548,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>58 plantor</t>
+          <t>På klen död gran vid lodyta.</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
@@ -5164,15 +4571,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>105312009</v>
+        <v>105312004</v>
       </c>
       <c r="B40" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5180,21 +4582,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5204,10 +4606,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>612237.4628812771</v>
+        <v>612405</v>
       </c>
       <c r="R40" t="n">
-        <v>6866697.804936196</v>
+        <v>6866856</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5237,19 +4639,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5281,15 +4673,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>105312003</v>
+        <v>105312021</v>
       </c>
       <c r="B41" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5297,21 +4684,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5321,10 +4708,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>612407.4494243169</v>
+        <v>612297</v>
       </c>
       <c r="R41" t="n">
-        <v>6866854.731693911</v>
+        <v>6866861</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5354,19 +4741,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5398,37 +4775,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>105315305</v>
+        <v>105312017</v>
       </c>
       <c r="B42" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5438,10 +4810,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>612461.5070025732</v>
+        <v>612200</v>
       </c>
       <c r="R42" t="n">
-        <v>6866847.558029503</v>
+        <v>6866829</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5471,21 +4843,11 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5494,6 +4856,11 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
@@ -5515,15 +4882,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>105312010</v>
+        <v>105312013</v>
       </c>
       <c r="B43" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5531,21 +4893,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5555,10 +4917,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>612210.7068221393</v>
+        <v>612191</v>
       </c>
       <c r="R43" t="n">
-        <v>6866664.395357661</v>
+        <v>6866695</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5588,21 +4950,11 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5611,6 +4963,11 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
@@ -5632,37 +4989,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>105312001</v>
+        <v>105316174</v>
       </c>
       <c r="B44" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5672,10 +5024,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>612478.1482166544</v>
+        <v>612395</v>
       </c>
       <c r="R44" t="n">
-        <v>6866872.620376247</v>
+        <v>6866869</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5705,21 +5057,11 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5728,6 +5070,11 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
@@ -5749,15 +5096,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>105315304</v>
+        <v>102248208</v>
       </c>
       <c r="B45" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5178</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5765,37 +5107,40 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>102204</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hälleberget, Hls</t>
+          <t>Nordanstig, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>612555.3288585788</v>
+        <v>612148</v>
       </c>
       <c r="R45" t="n">
-        <v>6866994.432134885</v>
+        <v>6866611</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5824,7 +5169,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5834,7 +5179,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spår på död grangren.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5845,16 +5195,11 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AS45" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -5866,37 +5211,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>105312024</v>
+        <v>105316175</v>
       </c>
       <c r="B46" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>105930</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5906,10 +5246,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>612407.516403654</v>
+        <v>612180</v>
       </c>
       <c r="R46" t="n">
-        <v>6866981.540525435</v>
+        <v>6866771</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5939,19 +5279,9 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5983,15 +5313,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>105315310</v>
+        <v>105316176</v>
       </c>
       <c r="B47" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5999,21 +5324,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6023,10 +5348,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>612474.9277376443</v>
+        <v>612514</v>
       </c>
       <c r="R47" t="n">
-        <v>6867041.745063409</v>
+        <v>6867065</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6056,21 +5381,11 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6082,7 +5397,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>På granlåga.</t>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
@@ -6102,6 +5417,113 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>105310363</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hälleberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>612556</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6866974</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Harmånger</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2022-07-14</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2022-07-14</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>58 plantor</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 568-2025 artfynd.xlsx
+++ b/artfynd/A 568-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311999</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312000</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312002</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312003</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312006</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312008</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312011</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312015</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312016</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312018</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312019</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312024</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312029</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312030</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312032</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312005</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2411,6 +2496,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315308</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2513,6 +2603,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315304</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2615,6 +2710,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315305</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2717,6 +2817,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315306</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2819,6 +2924,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315307</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2926,6 +3036,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315309</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3033,6 +3148,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315310</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3135,6 +3255,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311997</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3237,6 +3362,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311998</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3339,6 +3469,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312001</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3441,6 +3576,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312007</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3543,6 +3683,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312009</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3645,6 +3790,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312010</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3747,6 +3897,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312012</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3849,6 +4004,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312014</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3951,6 +4111,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312020</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4053,6 +4218,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312022</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4155,6 +4325,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312023</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4257,6 +4432,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312025</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4359,6 +4539,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312026</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4461,6 +4646,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312028</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4568,6 +4758,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312027</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4670,6 +4865,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312004</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4772,6 +4972,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312021</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4879,6 +5084,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312017</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4986,6 +5196,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312013</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5093,6 +5308,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105316174</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5208,6 +5428,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102248208</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5310,6 +5535,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105316175</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5417,6 +5647,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105316176</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5524,8 +5759,62 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310363</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>